--- a/jogos_2025-07-06.xlsx
+++ b/jogos_2025-07-06.xlsx
@@ -643,22 +643,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Central Coast II</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -669,83 +669,83 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.9</v>
+        <v>1.69</v>
       </c>
       <c r="M2" t="n">
-        <v>3.59</v>
+        <v>3.82</v>
       </c>
       <c r="N2" t="n">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="O2" t="n">
-        <v>3.5</v>
+        <v>2.14</v>
       </c>
       <c r="P2" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.55</v>
+        <v>4.85</v>
       </c>
       <c r="R2" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="S2" t="n">
-        <v>3.3</v>
+        <v>2.89</v>
       </c>
       <c r="T2" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="U2" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="V2" t="n">
         <v>1.02</v>
       </c>
       <c r="W2" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="X2" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="Z2" t="n">
         <v>2.05</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.33</v>
+        <v>2.62</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
+          <t>['23', '90']</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG2" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.35</v>
+        <v>2.3</v>
       </c>
       <c r="AI2" t="n">
-        <v>2.15</v>
+        <v>1.36</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.83</v>
+        <v>3.4</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45844.08333333334</v>
@@ -772,109 +772,109 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
         <v>1</v>
       </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.69</v>
+        <v>3.08</v>
       </c>
       <c r="M3" t="n">
-        <v>3.82</v>
+        <v>4.1</v>
       </c>
       <c r="N3" t="n">
-        <v>4</v>
+        <v>1.89</v>
       </c>
       <c r="O3" t="n">
-        <v>2.14</v>
+        <v>3.85</v>
       </c>
       <c r="P3" t="n">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.85</v>
+        <v>2.23</v>
       </c>
       <c r="R3" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="S3" t="n">
-        <v>2.89</v>
+        <v>3.8</v>
       </c>
       <c r="T3" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="U3" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="V3" t="n">
         <v>1.02</v>
       </c>
       <c r="W3" t="n">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="X3" t="n">
-        <v>4.3</v>
+        <v>5.8</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.61</v>
+        <v>1.43</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.05</v>
+        <v>2.62</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.62</v>
+        <v>1.89</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.45</v>
+        <v>1.81</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.67</v>
+        <v>1.42</v>
       </c>
       <c r="AD3" t="n">
-        <v>2</v>
+        <v>2.55</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>['23', '90']</t>
+          <t>['49']</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+2', '75', '90']</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.3</v>
+        <v>1.14</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.36</v>
+        <v>2.33</v>
       </c>
       <c r="AJ3" t="n">
-        <v>3.4</v>
+        <v>1.54</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45844.08333333334</v>
@@ -901,25 +901,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Central Coast II</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -927,83 +927,83 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.08</v>
+        <v>2.9</v>
       </c>
       <c r="M4" t="n">
-        <v>4.1</v>
+        <v>3.59</v>
       </c>
       <c r="N4" t="n">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="O4" t="n">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="P4" t="n">
-        <v>2.48</v>
+        <v>2.27</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.23</v>
+        <v>2.55</v>
       </c>
       <c r="R4" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="S4" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="T4" t="n">
         <v>2.1</v>
       </c>
       <c r="U4" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="V4" t="n">
         <v>1.02</v>
       </c>
       <c r="W4" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="X4" t="n">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.43</v>
+        <v>1.65</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.62</v>
+        <v>2.05</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.89</v>
+        <v>2.33</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.81</v>
+        <v>1.55</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>['49']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>['45+2', '75', '90']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.14</v>
+        <v>1.35</v>
       </c>
       <c r="AI4" t="n">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.54</v>
+        <v>1.83</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45844.08333333334</v>
@@ -1159,22 +1159,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1185,83 +1185,83 @@
         </is>
       </c>
       <c r="L6" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>['32', '63', '75']</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI6" t="n">
         <v>1.93</v>
       </c>
-      <c r="M6" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>4</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="X6" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>1.69</v>
-      </c>
       <c r="AJ6" t="n">
-        <v>2.45</v>
+        <v>2.18</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45844.29166666666</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,109 +1288,109 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Ehime</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
         <v>3</v>
       </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
       <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
         <v>1</v>
       </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.44</v>
+        <v>2.93</v>
       </c>
       <c r="M7" t="n">
-        <v>3.09</v>
+        <v>3.26</v>
       </c>
       <c r="N7" t="n">
-        <v>2.59</v>
+        <v>2.12</v>
       </c>
       <c r="O7" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P7" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.3</v>
+        <v>2.75</v>
       </c>
       <c r="R7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U7" t="n">
         <v>1.44</v>
       </c>
-      <c r="S7" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.33</v>
-      </c>
       <c r="V7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="X7" t="n">
-        <v>2.69</v>
+        <v>3.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.15</v>
+        <v>1.82</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.57</v>
+        <v>1.88</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.96</v>
+        <v>3.04</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>['32', '63', '75']</t>
+          <t>['90+7']</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['16', '72', '82']</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.44</v>
+        <v>1.61</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.93</v>
+        <v>2.3</v>
       </c>
       <c r="AJ7" t="n">
-        <v>2.18</v>
+        <v>1.73</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45844.29166666666</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,109 +1417,109 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ehime</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
         <v>1</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="O8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T8" t="n">
         <v>3</v>
       </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L8" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="M8" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="N8" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="O8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R8" t="n">
+      <c r="U8" t="n">
         <v>1.36</v>
       </c>
-      <c r="S8" t="n">
-        <v>3</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.44</v>
-      </c>
       <c r="V8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W8" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="X8" t="n">
-        <v>3.5</v>
+        <v>2.83</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.04</v>
+        <v>3.75</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>['90+7']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>['16', '72', '82']</t>
+          <t>['63']</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AI8" t="n">
-        <v>2.3</v>
+        <v>2.56</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45844.29166666666</v>
@@ -1546,19 +1546,19 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1572,49 +1572,49 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.29</v>
+        <v>1.93</v>
       </c>
       <c r="M9" t="n">
-        <v>3.21</v>
+        <v>3.16</v>
       </c>
       <c r="N9" t="n">
-        <v>1.98</v>
+        <v>3.5</v>
       </c>
       <c r="O9" t="n">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="P9" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="R9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U9" t="n">
         <v>1.4</v>
       </c>
-      <c r="S9" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.36</v>
-      </c>
       <c r="V9" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="X9" t="n">
-        <v>2.83</v>
+        <v>2.92</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AA9" t="n">
         <v>3.75</v>
@@ -1623,10 +1623,10 @@
         <v>1.19</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1635,20 +1635,20 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>['63']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH9" t="n">
         <v>1.75</v>
       </c>
-      <c r="AH9" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AI9" t="n">
-        <v>2.56</v>
+        <v>1.69</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.66</v>
+        <v>2.45</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45844.29166666666</v>
@@ -1675,23 +1675,23 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
         <v>2</v>
       </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
@@ -1701,83 +1701,83 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>6.9</v>
+        <v>1.4</v>
       </c>
       <c r="M10" t="n">
-        <v>4.74</v>
+        <v>4</v>
       </c>
       <c r="N10" t="n">
-        <v>1.3</v>
+        <v>7.77</v>
       </c>
       <c r="O10" t="n">
-        <v>7.5</v>
+        <v>1.72</v>
       </c>
       <c r="P10" t="n">
-        <v>2.43</v>
+        <v>2.35</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.78</v>
+        <v>6.7</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S10" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="T10" t="n">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="U10" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="V10" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W10" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X10" t="n">
         <v>3.8</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
+          <t>['29', '45+1', '77', '81']</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>['63', '54']</t>
-        </is>
-      </c>
       <c r="AG10" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.06</v>
+        <v>2.41</v>
       </c>
       <c r="AI10" t="n">
-        <v>4.33</v>
+        <v>1.25</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.25</v>
+        <v>4.75</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45844.35416666666</v>
@@ -1804,19 +1804,19 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Foshan Nanshi</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1830,83 +1830,83 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['86']</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+1']</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45844.35416666666</v>
@@ -1933,16 +1933,16 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>1</v>
@@ -1959,46 +1959,46 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.95</v>
+        <v>4.43</v>
       </c>
       <c r="M12" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N12" t="n">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="O12" t="n">
-        <v>2.6</v>
+        <v>5.26</v>
       </c>
       <c r="P12" t="n">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="Q12" t="n">
-        <v>4</v>
+        <v>2.29</v>
       </c>
       <c r="R12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U12" t="n">
         <v>1.38</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.33</v>
       </c>
       <c r="V12" t="n">
         <v>1.04</v>
       </c>
       <c r="W12" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="X12" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.09</v>
+        <v>1.95</v>
       </c>
       <c r="Z12" t="n">
         <v>1.75</v>
@@ -2007,35 +2007,35 @@
         <v>3.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AC12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD12" t="n">
         <v>1.8</v>
       </c>
-      <c r="AD12" t="n">
-        <v>1.86</v>
-      </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>['86']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>['90+1']</t>
+          <t>['61']</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.69</v>
+        <v>1.1</v>
       </c>
       <c r="AI12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AJ12" t="n">
         <v>1.67</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>2.4</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45844.35416666666</v>
@@ -2062,19 +2062,19 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Foshan Nanshi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>5.26</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2151,20 +2151,20 @@
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>['61']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45844.35416666666</v>
@@ -2191,22 +2191,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -2217,83 +2217,83 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.4</v>
+        <v>6.9</v>
       </c>
       <c r="M14" t="n">
-        <v>4</v>
+        <v>4.74</v>
       </c>
       <c r="N14" t="n">
-        <v>7.77</v>
+        <v>1.3</v>
       </c>
       <c r="O14" t="n">
-        <v>1.72</v>
+        <v>7.5</v>
       </c>
       <c r="P14" t="n">
-        <v>2.35</v>
+        <v>2.43</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.7</v>
+        <v>1.78</v>
       </c>
       <c r="R14" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="S14" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="T14" t="n">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="U14" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="V14" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W14" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X14" t="n">
         <v>3.8</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AC14" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>['29', '45+1', '77', '81']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['63', '54']</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.41</v>
+        <v>1.06</v>
       </c>
       <c r="AI14" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AJ14" t="n">
         <v>1.25</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>4.75</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45844.35416666666</v>
@@ -3739,25 +3739,25 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -3765,83 +3765,83 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="M26" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="N26" t="n">
-        <v>3.38</v>
+        <v>3.64</v>
       </c>
       <c r="O26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P26" t="n">
         <v>2.3</v>
       </c>
-      <c r="P26" t="n">
-        <v>2.4</v>
-      </c>
       <c r="Q26" t="n">
-        <v>4.33</v>
+        <v>5.5</v>
       </c>
       <c r="R26" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="S26" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="T26" t="n">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="U26" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="V26" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W26" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="X26" t="n">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.55</v>
+        <v>1.82</v>
       </c>
       <c r="Z26" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>['10', '24', '26', '53', '88']</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>['51']</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AH26" t="n">
         <v>2.2</v>
       </c>
-      <c r="AA26" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>['33', '90+3']</t>
-        </is>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AI26" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45844.47916666666</v>
@@ -3868,109 +3868,109 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
+        <v>2</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
         <v>1</v>
       </c>
-      <c r="I27" t="n">
-        <v>3</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
       <c r="K27" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="M27" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="O27" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S27" t="n">
         <v>3.5</v>
       </c>
-      <c r="N27" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="O27" t="n">
+      <c r="T27" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X27" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z27" t="n">
         <v>2.2</v>
       </c>
-      <c r="P27" t="n">
+      <c r="AA27" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q27" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S27" t="n">
-        <v>3</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X27" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>3.1</v>
-      </c>
       <c r="AB27" t="n">
-        <v>1.38</v>
+        <v>1.54</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>['10', '24', '26', '53', '88']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>['51']</t>
+          <t>['33', '90+3']</t>
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AJ27" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45844.47916666666</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,16 +3997,16 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -4023,65 +4023,65 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="M28" t="n">
-        <v>3.79</v>
+        <v>3.49</v>
       </c>
       <c r="N28" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="O28" t="n">
-        <v>2.33</v>
+        <v>2.49</v>
       </c>
       <c r="P28" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.25</v>
+        <v>3.83</v>
       </c>
       <c r="R28" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="S28" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="T28" t="n">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="U28" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="V28" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W28" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="X28" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="Y28" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC28" t="n">
         <v>1.67</v>
       </c>
-      <c r="Z28" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AD28" t="n">
-        <v>2.15</v>
+        <v>1.94</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>['15']</t>
+          <t>['22', '65']</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
@@ -4090,7 +4090,7 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH28" t="n">
         <v>1.83</v>
@@ -4099,7 +4099,7 @@
         <v>1.5</v>
       </c>
       <c r="AJ28" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45844.5</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,16 +4126,16 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -4152,65 +4152,65 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="M29" t="n">
-        <v>3.49</v>
+        <v>3.79</v>
       </c>
       <c r="N29" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="O29" t="n">
-        <v>2.49</v>
+        <v>2.33</v>
       </c>
       <c r="P29" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X29" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z29" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q29" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S29" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="X29" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AA29" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>['22', '65']</t>
+          <t>['15']</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH29" t="n">
         <v>1.83</v>
@@ -4228,7 +4228,7 @@
         <v>1.5</v>
       </c>
       <c r="AJ29" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45844.5</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,22 +4513,22 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J32" t="n">
         <v>1</v>
@@ -4539,83 +4539,83 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>4.09</v>
+        <v>2.2</v>
       </c>
       <c r="M32" t="n">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="N32" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="O32" t="n">
-        <v>3.95</v>
+        <v>2.45</v>
       </c>
       <c r="P32" t="n">
-        <v>2.37</v>
+        <v>2.05</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.35</v>
+        <v>3.8</v>
       </c>
       <c r="R32" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X32" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="AB32" t="n">
         <v>1.2</v>
       </c>
-      <c r="S32" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X32" t="n">
-        <v>5.43</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AC32" t="n">
-        <v>1.44</v>
+        <v>1.83</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.5</v>
+        <v>1.83</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['10', '19', '7', '47']</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>['23']</t>
+          <t>['44', '90+3']</t>
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="AI32" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45844.52083333334</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,22 +4642,22 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
         <v>1</v>
@@ -4668,83 +4668,83 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.2</v>
+        <v>4.09</v>
       </c>
       <c r="M33" t="n">
-        <v>3.15</v>
+        <v>4</v>
       </c>
       <c r="N33" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="O33" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X33" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z33" t="n">
         <v>2.45</v>
       </c>
-      <c r="P33" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S33" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T33" t="n">
+      <c r="AA33" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>['23']</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI33" t="n">
         <v>2.75</v>
       </c>
-      <c r="U33" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X33" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>['10', '19', '7', '47']</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>['44', '90+3']</t>
-        </is>
-      </c>
-      <c r="AG33" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45844.52083333334</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,25 +4771,25 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G34" t="n">
         <v>1</v>
       </c>
       <c r="H34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -4797,83 +4797,83 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.06</v>
+        <v>1.68</v>
       </c>
       <c r="M34" t="n">
-        <v>12.37</v>
+        <v>4.55</v>
       </c>
       <c r="N34" t="n">
-        <v>29.65</v>
+        <v>3.75</v>
       </c>
       <c r="O34" t="n">
-        <v>1.22</v>
+        <v>2.23</v>
       </c>
       <c r="P34" t="n">
-        <v>3.8</v>
+        <v>2.66</v>
       </c>
       <c r="Q34" t="n">
-        <v>15</v>
+        <v>3.4</v>
       </c>
       <c r="R34" t="n">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="T34" t="n">
-        <v>1.75</v>
+        <v>1.98</v>
       </c>
       <c r="U34" t="n">
-        <v>2.15</v>
+        <v>1.97</v>
       </c>
       <c r="V34" t="n">
         <v>1.01</v>
       </c>
       <c r="W34" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X34" t="n">
-        <v>5.3</v>
+        <v>7.5</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.2</v>
+        <v>1.36</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>['84']</t>
+          <t>['71']</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>['20']</t>
+          <t>['69', '65']</t>
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.06</v>
+        <v>1.22</v>
       </c>
       <c r="AH34" t="n">
-        <v>9.5</v>
+        <v>2</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.14</v>
+        <v>1.57</v>
       </c>
       <c r="AJ34" t="n">
-        <v>5.5</v>
+        <v>2.26</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45844.54166666666</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,25 +4900,25 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G35" t="n">
         <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -4926,83 +4926,83 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.68</v>
+        <v>1.06</v>
       </c>
       <c r="M35" t="n">
-        <v>4.55</v>
+        <v>12.37</v>
       </c>
       <c r="N35" t="n">
-        <v>3.75</v>
+        <v>29.65</v>
       </c>
       <c r="O35" t="n">
-        <v>2.23</v>
+        <v>1.22</v>
       </c>
       <c r="P35" t="n">
-        <v>2.66</v>
+        <v>3.8</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.4</v>
+        <v>15</v>
       </c>
       <c r="R35" t="n">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="S35" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="T35" t="n">
-        <v>1.98</v>
+        <v>1.75</v>
       </c>
       <c r="U35" t="n">
-        <v>1.97</v>
+        <v>2.15</v>
       </c>
       <c r="V35" t="n">
         <v>1.01</v>
       </c>
       <c r="W35" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X35" t="n">
-        <v>7.5</v>
+        <v>5.3</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z35" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.36</v>
+        <v>2.2</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>['71']</t>
+          <t>['84']</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>['69', '65']</t>
+          <t>['20']</t>
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="AH35" t="n">
-        <v>2</v>
+        <v>9.5</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.57</v>
+        <v>1.14</v>
       </c>
       <c r="AJ35" t="n">
-        <v>2.26</v>
+        <v>5.5</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45844.54166666666</v>
@@ -5674,16 +5674,16 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Gimnasia Mendoza</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -5696,32 +5696,32 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.87</v>
+        <v>1.6</v>
       </c>
       <c r="M41" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="N41" t="n">
-        <v>4.15</v>
+        <v>5.93</v>
       </c>
       <c r="O41" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="P41" t="n">
-        <v>1.93</v>
+        <v>1.7</v>
       </c>
       <c r="Q41" t="n">
-        <v>5.75</v>
+        <v>6.2</v>
       </c>
       <c r="R41" t="n">
         <v>1.6</v>
       </c>
       <c r="S41" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="T41" t="n">
         <v>3.8</v>
@@ -5730,35 +5730,35 @@
         <v>1.22</v>
       </c>
       <c r="V41" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X41" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AB41" t="n">
         <v>1.12</v>
       </c>
-      <c r="W41" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="X41" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AC41" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AD41" t="n">
         <v>1.5</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['70']</t>
         </is>
       </c>
       <c r="AF41" t="inlineStr">
@@ -5770,13 +5770,13 @@
         <v>1.33</v>
       </c>
       <c r="AH41" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AJ41" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AK41" s="3" t="n">
         <v>45844.64583333334</v>
@@ -5803,16 +5803,16 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Gimnasia Mendoza</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -5825,32 +5825,32 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.6</v>
+        <v>1.87</v>
       </c>
       <c r="M42" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N42" t="n">
-        <v>5.93</v>
+        <v>4.15</v>
       </c>
       <c r="O42" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="P42" t="n">
-        <v>1.7</v>
+        <v>1.93</v>
       </c>
       <c r="Q42" t="n">
-        <v>6.2</v>
+        <v>5.75</v>
       </c>
       <c r="R42" t="n">
         <v>1.6</v>
       </c>
       <c r="S42" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="T42" t="n">
         <v>3.8</v>
@@ -5859,35 +5859,35 @@
         <v>1.22</v>
       </c>
       <c r="V42" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="W42" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="X42" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AA42" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AD42" t="n">
         <v>1.5</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>['70']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
@@ -5899,13 +5899,13 @@
         <v>1.33</v>
       </c>
       <c r="AH42" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AJ42" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AK42" s="3" t="n">
         <v>45844.64583333334</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,22 +6319,22 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
         <v>1</v>
@@ -6345,83 +6345,83 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.68</v>
+        <v>2.3</v>
       </c>
       <c r="M46" t="n">
-        <v>4.35</v>
+        <v>2.8</v>
       </c>
       <c r="N46" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="O46" t="n">
-        <v>2.16</v>
+        <v>2.95</v>
       </c>
       <c r="P46" t="n">
-        <v>2.43</v>
+        <v>1.79</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.1</v>
+        <v>4.56</v>
       </c>
       <c r="R46" t="n">
-        <v>1.2</v>
+        <v>1.55</v>
       </c>
       <c r="S46" t="n">
-        <v>3.9</v>
+        <v>2.25</v>
       </c>
       <c r="T46" t="n">
-        <v>2.06</v>
+        <v>3.55</v>
       </c>
       <c r="U46" t="n">
-        <v>1.71</v>
+        <v>1.24</v>
       </c>
       <c r="V46" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W46" t="n">
-        <v>1.07</v>
+        <v>1.61</v>
       </c>
       <c r="X46" t="n">
-        <v>5.85</v>
+        <v>2.36</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.36</v>
+        <v>2.55</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.69</v>
+        <v>1.45</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.98</v>
+        <v>5.65</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.75</v>
+        <v>1.13</v>
       </c>
       <c r="AC46" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>['12']</t>
+        </is>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>['3', '61', '90+9']</t>
+        </is>
+      </c>
+      <c r="AG46" t="n">
         <v>1.4</v>
       </c>
-      <c r="AD46" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AE46" t="inlineStr">
-        <is>
-          <t>['3', '6', '47', '51', '58', '65', '68']</t>
-        </is>
-      </c>
-      <c r="AF46" t="inlineStr">
-        <is>
-          <t>['35', '70']</t>
-        </is>
-      </c>
-      <c r="AG46" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AH46" t="n">
-        <v>2.02</v>
+        <v>1.57</v>
       </c>
       <c r="AI46" t="n">
-        <v>1.53</v>
+        <v>1.93</v>
       </c>
       <c r="AJ46" t="n">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="AK46" s="3" t="n">
         <v>45844.66666666666</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,22 +6448,22 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -6474,65 +6474,65 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.4</v>
+        <v>3.8</v>
       </c>
       <c r="M47" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="N47" t="n">
-        <v>6</v>
+        <v>1.9</v>
       </c>
       <c r="O47" t="n">
-        <v>1.9</v>
+        <v>4.75</v>
       </c>
       <c r="P47" t="n">
-        <v>2.46</v>
+        <v>2.05</v>
       </c>
       <c r="Q47" t="n">
-        <v>5.3</v>
+        <v>2.6</v>
       </c>
       <c r="R47" t="n">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="S47" t="n">
-        <v>3.4</v>
+        <v>2.63</v>
       </c>
       <c r="T47" t="n">
-        <v>2.1</v>
+        <v>3.25</v>
       </c>
       <c r="U47" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="V47" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="W47" t="n">
-        <v>1.14</v>
+        <v>1.35</v>
       </c>
       <c r="X47" t="n">
-        <v>4.4</v>
+        <v>2.75</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.47</v>
+        <v>2.2</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.2</v>
+        <v>1.65</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.55</v>
+        <v>3.82</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.56</v>
+        <v>1.19</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AD47" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>['27', '63', '78', '90+14', '90+4']</t>
+          <t>['70', '90+5']</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
@@ -6541,16 +6541,16 @@
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.13</v>
+        <v>1.85</v>
       </c>
       <c r="AH47" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI47" t="n">
         <v>2.75</v>
       </c>
-      <c r="AI47" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AJ47" t="n">
-        <v>3.1</v>
+        <v>1.57</v>
       </c>
       <c r="AK47" s="3" t="n">
         <v>45844.66666666666</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,22 +6577,22 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J48" t="n">
         <v>1</v>
@@ -6603,83 +6603,83 @@
         </is>
       </c>
       <c r="L48" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="M48" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="N48" t="n">
+        <v>4</v>
+      </c>
+      <c r="O48" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="P48" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S48" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X48" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z48" t="n">
         <v>2.69</v>
       </c>
-      <c r="M48" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N48" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="O48" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="P48" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="R48" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S48" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T48" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="U48" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V48" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W48" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X48" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>1.82</v>
-      </c>
       <c r="AA48" t="n">
-        <v>3.4</v>
+        <v>1.98</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.29</v>
+        <v>1.75</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AD48" t="n">
-        <v>2</v>
+        <v>2.64</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['3', '6', '47', '51', '58', '65', '68']</t>
         </is>
       </c>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>['13']</t>
+          <t>['35', '70']</t>
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.44</v>
+        <v>2.02</v>
       </c>
       <c r="AI48" t="n">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="AJ48" t="n">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="AK48" s="3" t="n">
         <v>45844.66666666666</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Paraguay Division Profesional</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,19 +6706,19 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Olimpia</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Nacional Asunción</t>
         </is>
       </c>
       <c r="G49" t="n">
         <v>1</v>
       </c>
       <c r="H49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I49" t="n">
         <v>1</v>
@@ -6732,83 +6732,83 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.3</v>
+        <v>2.13</v>
       </c>
       <c r="M49" t="n">
-        <v>2.8</v>
+        <v>2.93</v>
       </c>
       <c r="N49" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="O49" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="P49" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.56</v>
+        <v>4.1</v>
       </c>
       <c r="R49" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="S49" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="T49" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="U49" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="V49" t="n">
         <v>1.06</v>
       </c>
       <c r="W49" t="n">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="X49" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="Y49" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="AA49" t="n">
-        <v>5.65</v>
+        <v>4.7</v>
       </c>
       <c r="AB49" t="n">
         <v>1.13</v>
       </c>
       <c r="AC49" t="n">
-        <v>2.21</v>
+        <v>2.05</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
+          <t>['31']</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
           <t>['12']</t>
         </is>
       </c>
-      <c r="AF49" t="inlineStr">
-        <is>
-          <t>['3', '61', '90+9']</t>
-        </is>
-      </c>
       <c r="AG49" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AI49" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AJ49" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AK49" s="3" t="n">
         <v>45844.66666666666</v>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,109 +6964,109 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="M51" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N51" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O51" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P51" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S51" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V51" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W51" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X51" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Y51" t="n">
         <v>2</v>
       </c>
-      <c r="H51" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L51" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="M51" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="N51" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="O51" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="P51" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R51" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="S51" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="T51" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="U51" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="V51" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W51" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="X51" t="n">
+      <c r="Z51" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD51" t="n">
         <v>2</v>
       </c>
-      <c r="Y51" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AE51" t="inlineStr">
         <is>
-          <t>['62', '67']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['13']</t>
         </is>
       </c>
       <c r="AG51" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AH51" t="n">
-        <v>1.72</v>
+        <v>1.44</v>
       </c>
       <c r="AI51" t="n">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="AJ51" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="AK51" s="3" t="n">
         <v>45844.66666666666</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Paraguay Division Profesional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,109 +7222,109 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Olimpia</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Nacional Asunción</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
         <v>1</v>
       </c>
       <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M53" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N53" t="n">
+        <v>6</v>
+      </c>
+      <c r="O53" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="P53" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="R53" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S53" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V53" t="n">
         <v>1</v>
       </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L53" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="M53" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="N53" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O53" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="P53" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="R53" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S53" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T53" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U53" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V53" t="n">
-        <v>1.06</v>
-      </c>
       <c r="W53" t="n">
-        <v>1.44</v>
+        <v>1.14</v>
       </c>
       <c r="X53" t="n">
-        <v>2.5</v>
+        <v>4.4</v>
       </c>
       <c r="Y53" t="n">
-        <v>2.4</v>
+        <v>1.47</v>
       </c>
       <c r="Z53" t="n">
-        <v>1.51</v>
+        <v>2.2</v>
       </c>
       <c r="AA53" t="n">
-        <v>4.7</v>
+        <v>2.55</v>
       </c>
       <c r="AB53" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>['27', '63', '78', '90+14', '90+4']</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG53" t="n">
         <v>1.13</v>
       </c>
-      <c r="AC53" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE53" t="inlineStr">
-        <is>
-          <t>['31']</t>
-        </is>
-      </c>
-      <c r="AF53" t="inlineStr">
-        <is>
-          <t>['12']</t>
-        </is>
-      </c>
-      <c r="AG53" t="n">
+      <c r="AH53" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AI53" t="n">
         <v>1.36</v>
       </c>
-      <c r="AH53" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AI53" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ53" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AK53" s="3" t="n">
         <v>45844.66666666666</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,65 +7377,65 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>3.8</v>
+        <v>2.2</v>
       </c>
       <c r="M54" t="n">
-        <v>3.6</v>
+        <v>2.81</v>
       </c>
       <c r="N54" t="n">
-        <v>1.9</v>
+        <v>3.68</v>
       </c>
       <c r="O54" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="P54" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q54" t="n">
         <v>4.75</v>
       </c>
-      <c r="P54" t="n">
+      <c r="R54" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="S54" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q54" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R54" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S54" t="n">
-        <v>2.63</v>
-      </c>
       <c r="T54" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="V54" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W54" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="X54" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y54" t="n">
         <v>3.25</v>
       </c>
-      <c r="U54" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V54" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W54" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X54" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>2.2</v>
-      </c>
       <c r="Z54" t="n">
-        <v>1.65</v>
+        <v>1.3</v>
       </c>
       <c r="AA54" t="n">
-        <v>3.82</v>
+        <v>6.9</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.19</v>
+        <v>1.09</v>
       </c>
       <c r="AC54" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.73</v>
+        <v>1.48</v>
       </c>
       <c r="AE54" t="inlineStr">
         <is>
-          <t>['70', '90+5']</t>
+          <t>['62', '67']</t>
         </is>
       </c>
       <c r="AF54" t="inlineStr">
@@ -7444,16 +7444,16 @@
         </is>
       </c>
       <c r="AG54" t="n">
-        <v>1.85</v>
+        <v>1.37</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.22</v>
+        <v>1.72</v>
       </c>
       <c r="AI54" t="n">
-        <v>2.75</v>
+        <v>1.62</v>
       </c>
       <c r="AJ54" t="n">
-        <v>1.57</v>
+        <v>3.2</v>
       </c>
       <c r="AK54" s="3" t="n">
         <v>45844.66666666666</v>
@@ -8151,61 +8151,61 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="M60" t="n">
-        <v>3.95</v>
+        <v>3.41</v>
       </c>
       <c r="N60" t="n">
-        <v>3.55</v>
+        <v>3.47</v>
       </c>
       <c r="O60" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="P60" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="R60" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S60" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="T60" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="U60" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="V60" t="n">
         <v>1.01</v>
       </c>
       <c r="W60" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X60" t="n">
-        <v>5.2</v>
+        <v>4.05</v>
       </c>
       <c r="Y60" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="Z60" t="n">
-        <v>2.53</v>
+        <v>2.3</v>
       </c>
       <c r="AA60" t="n">
-        <v>2.25</v>
+        <v>2.9</v>
       </c>
       <c r="AB60" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC60" t="n">
         <v>1.62</v>
       </c>
-      <c r="AC60" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AD60" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="AE60" t="inlineStr">
         <is>
@@ -8218,16 +8218,16 @@
         </is>
       </c>
       <c r="AG60" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH60" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AI60" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AJ60" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AK60" s="3" t="n">
         <v>45844.75</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Paraguay Division Profesional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,22 +8383,22 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Guaraní</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2 de Mayo</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H62" t="n">
         <v>1</v>
       </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -8409,83 +8409,83 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.28</v>
+        <v>1.68</v>
       </c>
       <c r="M62" t="n">
-        <v>2.92</v>
+        <v>3.9</v>
       </c>
       <c r="N62" t="n">
-        <v>3.18</v>
+        <v>4.25</v>
       </c>
       <c r="O62" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="P62" t="n">
-        <v>1.83</v>
+        <v>2.39</v>
       </c>
       <c r="Q62" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="R62" t="n">
-        <v>1.57</v>
+        <v>1.24</v>
       </c>
       <c r="S62" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="T62" t="n">
         <v>2.25</v>
       </c>
-      <c r="T62" t="n">
-        <v>3.3</v>
-      </c>
       <c r="U62" t="n">
-        <v>1.27</v>
+        <v>1.6</v>
       </c>
       <c r="V62" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="W62" t="n">
-        <v>1.49</v>
+        <v>1.12</v>
       </c>
       <c r="X62" t="n">
-        <v>2.4</v>
+        <v>4.75</v>
       </c>
       <c r="Y62" t="n">
-        <v>2.6</v>
+        <v>1.56</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="AA62" t="n">
-        <v>4.75</v>
+        <v>2.31</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.15</v>
+        <v>1.55</v>
       </c>
       <c r="AC62" t="n">
-        <v>2.05</v>
+        <v>1.53</v>
       </c>
       <c r="AD62" t="n">
-        <v>1.72</v>
+        <v>2.27</v>
       </c>
       <c r="AE62" t="inlineStr">
         <is>
-          <t>['45+1', '79', '90+5']</t>
+          <t>['19', '29', '33', '65', '72']</t>
         </is>
       </c>
       <c r="AF62" t="inlineStr">
         <is>
-          <t>['59']</t>
+          <t>['87']</t>
         </is>
       </c>
       <c r="AG62" t="n">
-        <v>1.4</v>
+        <v>1.16</v>
       </c>
       <c r="AH62" t="n">
-        <v>1.57</v>
+        <v>2.13</v>
       </c>
       <c r="AI62" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AJ62" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AK62" s="3" t="n">
         <v>45844.77083333334</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Paraguay Division Profesional</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,22 +8641,22 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Guaraní</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>2 de Mayo</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -8667,83 +8667,83 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>3.45</v>
+        <v>2.28</v>
       </c>
       <c r="M64" t="n">
-        <v>2.78</v>
+        <v>2.92</v>
       </c>
       <c r="N64" t="n">
-        <v>2.32</v>
+        <v>3.18</v>
       </c>
       <c r="O64" t="n">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="P64" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.27</v>
+        <v>4</v>
       </c>
       <c r="R64" t="n">
-        <v>1.74</v>
+        <v>1.57</v>
       </c>
       <c r="S64" t="n">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="T64" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="U64" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="V64" t="n">
         <v>1.11</v>
       </c>
       <c r="W64" t="n">
-        <v>1.75</v>
+        <v>1.49</v>
       </c>
       <c r="X64" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="Y64" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="AA64" t="n">
-        <v>5.8</v>
+        <v>4.75</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AC64" t="n">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="AD64" t="n">
-        <v>1.48</v>
+        <v>1.72</v>
       </c>
       <c r="AE64" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+1', '79', '90+5']</t>
         </is>
       </c>
       <c r="AF64" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['59']</t>
         </is>
       </c>
       <c r="AG64" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AH64" t="n">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="AI64" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AJ64" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AK64" s="3" t="n">
         <v>45844.77083333334</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,22 +8770,22 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -8796,83 +8796,83 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.68</v>
+        <v>3.45</v>
       </c>
       <c r="M65" t="n">
-        <v>3.9</v>
+        <v>2.78</v>
       </c>
       <c r="N65" t="n">
-        <v>4.25</v>
+        <v>2.32</v>
       </c>
       <c r="O65" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="P65" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="R65" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="S65" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="T65" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V65" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W65" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="X65" t="n">
         <v>2.1</v>
       </c>
-      <c r="P65" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R65" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S65" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="T65" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U65" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V65" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W65" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X65" t="n">
-        <v>4.75</v>
-      </c>
       <c r="Y65" t="n">
-        <v>1.56</v>
+        <v>3.5</v>
       </c>
       <c r="Z65" t="n">
-        <v>2.3</v>
+        <v>1.28</v>
       </c>
       <c r="AA65" t="n">
-        <v>2.31</v>
+        <v>5.8</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.55</v>
+        <v>1.09</v>
       </c>
       <c r="AC65" t="n">
-        <v>1.53</v>
+        <v>2.45</v>
       </c>
       <c r="AD65" t="n">
-        <v>2.27</v>
+        <v>1.48</v>
       </c>
       <c r="AE65" t="inlineStr">
         <is>
-          <t>['19', '29', '33', '65', '72']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF65" t="inlineStr">
         <is>
-          <t>['87']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG65" t="n">
-        <v>1.16</v>
+        <v>1.45</v>
       </c>
       <c r="AH65" t="n">
-        <v>2.13</v>
+        <v>1.3</v>
       </c>
       <c r="AI65" t="n">
-        <v>1.48</v>
+        <v>2.45</v>
       </c>
       <c r="AJ65" t="n">
-        <v>2.59</v>
+        <v>1.93</v>
       </c>
       <c r="AK65" s="3" t="n">
         <v>45844.77083333334</v>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,22 +9028,22 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H67" t="n">
         <v>2</v>
       </c>
       <c r="I67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J67" t="n">
         <v>1</v>
@@ -9054,83 +9054,83 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.95</v>
+        <v>2.88</v>
       </c>
       <c r="M67" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="N67" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="O67" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="P67" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="R67" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="S67" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T67" t="n">
         <v>3.7</v>
       </c>
-      <c r="N67" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O67" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="P67" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="Q67" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="R67" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S67" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T67" t="n">
-        <v>2.25</v>
-      </c>
       <c r="U67" t="n">
-        <v>1.57</v>
+        <v>1.2</v>
       </c>
       <c r="V67" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="W67" t="n">
-        <v>1.2</v>
+        <v>1.61</v>
       </c>
       <c r="X67" t="n">
-        <v>4.3</v>
+        <v>2.1</v>
       </c>
       <c r="Y67" t="n">
-        <v>1.55</v>
+        <v>2.95</v>
       </c>
       <c r="Z67" t="n">
-        <v>2.2</v>
+        <v>1.36</v>
       </c>
       <c r="AA67" t="n">
-        <v>2.5</v>
+        <v>5.75</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.47</v>
+        <v>1.11</v>
       </c>
       <c r="AC67" t="n">
-        <v>1.57</v>
+        <v>2.32</v>
       </c>
       <c r="AD67" t="n">
-        <v>2.56</v>
+        <v>1.53</v>
       </c>
       <c r="AE67" t="inlineStr">
         <is>
-          <t>['58', '43']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF67" t="inlineStr">
         <is>
-          <t>['45+1', '51']</t>
+          <t>['38', '56']</t>
         </is>
       </c>
       <c r="AG67" t="n">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="AH67" t="n">
-        <v>1.75</v>
+        <v>1.35</v>
       </c>
       <c r="AI67" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AJ67" t="n">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="AK67" s="3" t="n">
         <v>45844.79166666666</v>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,22 +9157,22 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H68" t="n">
         <v>2</v>
       </c>
       <c r="I68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J68" t="n">
         <v>1</v>
@@ -9183,83 +9183,83 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.88</v>
+        <v>1.95</v>
       </c>
       <c r="M68" t="n">
-        <v>2.72</v>
+        <v>3.7</v>
       </c>
       <c r="N68" t="n">
-        <v>2.52</v>
+        <v>3.2</v>
       </c>
       <c r="O68" t="n">
-        <v>4.1</v>
+        <v>2.42</v>
       </c>
       <c r="P68" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R68" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S68" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V68" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W68" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X68" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD68" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AE68" t="inlineStr">
+        <is>
+          <t>['58', '43']</t>
+        </is>
+      </c>
+      <c r="AF68" t="inlineStr">
+        <is>
+          <t>['45+1', '51']</t>
+        </is>
+      </c>
+      <c r="AG68" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AH68" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI68" t="n">
         <v>1.73</v>
       </c>
-      <c r="Q68" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="R68" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="S68" t="n">
+      <c r="AJ68" t="n">
         <v>2.1</v>
-      </c>
-      <c r="T68" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="U68" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V68" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W68" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="X68" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Y68" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="Z68" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AA68" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AB68" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AC68" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AD68" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF68" t="inlineStr">
-        <is>
-          <t>['38', '56']</t>
-        </is>
-      </c>
-      <c r="AG68" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AH68" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AI68" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AJ68" t="n">
-        <v>2.75</v>
       </c>
       <c r="AK68" s="3" t="n">
         <v>45844.79166666666</v>
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,19 +9415,19 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I70" t="n">
         <v>0</v>
@@ -9441,83 +9441,83 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="S70" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T70" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="U70" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="V70" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W70" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X70" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z70" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC70" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AD70" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AE70" t="inlineStr">
         <is>
-          <t>['49', '64']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF70" t="inlineStr">
         <is>
-          <t>['30', '79']</t>
+          <t>['37', '59', '67', '87']</t>
         </is>
       </c>
       <c r="AG70" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH70" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AI70" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AJ70" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AK70" s="3" t="n">
         <v>45844.83333333334</v>
@@ -9544,109 +9544,109 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H71" t="n">
         <v>2</v>
       </c>
       <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="n">
         <v>1</v>
       </c>
-      <c r="J71" t="n">
-        <v>0</v>
-      </c>
       <c r="K71" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="M71" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N71" t="n">
         <v>3.7</v>
       </c>
-      <c r="N71" t="n">
-        <v>2.87</v>
-      </c>
       <c r="O71" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="P71" t="n">
-        <v>2.36</v>
+        <v>2.45</v>
       </c>
       <c r="Q71" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="R71" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="S71" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="T71" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="U71" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="V71" t="n">
         <v>1.02</v>
       </c>
       <c r="W71" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X71" t="n">
         <v>5.5</v>
       </c>
       <c r="Y71" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC71" t="n">
         <v>1.44</v>
       </c>
-      <c r="Z71" t="n">
+      <c r="AD71" t="n">
         <v>2.66</v>
       </c>
-      <c r="AA71" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB71" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AC71" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AD71" t="n">
-        <v>2.75</v>
-      </c>
       <c r="AE71" t="inlineStr">
         <is>
-          <t>['26']</t>
+          <t>['49', '64']</t>
         </is>
       </c>
       <c r="AF71" t="inlineStr">
         <is>
-          <t>['83', '72']</t>
+          <t>['30', '79']</t>
         </is>
       </c>
       <c r="AG71" t="n">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="AH71" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AI71" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AJ71" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AK71" s="3" t="n">
         <v>45844.83333333334</v>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,25 +9673,25 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H72" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -9699,83 +9699,83 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O72" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S72" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T72" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U72" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V72" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W72" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X72" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="Y72" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z72" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AA72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC72" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AD72" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AE72" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['26']</t>
         </is>
       </c>
       <c r="AF72" t="inlineStr">
         <is>
-          <t>['37', '59', '67', '87']</t>
+          <t>['83', '72']</t>
         </is>
       </c>
       <c r="AG72" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AH72" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI72" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AJ72" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AK72" s="3" t="n">
         <v>45844.83333333334</v>
